--- a/artfynd/A 37219-2026 artfynd.xlsx
+++ b/artfynd/A 37219-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>135975617</v>
       </c>
       <c r="B6" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135975845</v>
       </c>
       <c r="B7" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>135975623</v>
       </c>
       <c r="B10" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>135975749</v>
       </c>
       <c r="B11" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>135975605</v>
       </c>
       <c r="B12" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
